--- a/Shiny/Datos limpios/pricing_semanal_sorgo_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_sorgo_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -2202,16 +2202,16 @@
         <v>45943</v>
       </c>
       <c r="D43">
-        <v>22180.73</v>
+        <v>21680.73</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G43">
-        <v>21680.73</v>
+        <v>20680.73</v>
       </c>
       <c r="H43">
         <v>958.13</v>
@@ -2226,7 +2226,7 @@
         <v>958.13</v>
       </c>
       <c r="L43">
-        <v>22638.86</v>
+        <v>21638.86</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2272,6 +2272,178 @@
         <v>7764.790000000001</v>
       </c>
       <c r="M44" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2025</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2">
+        <v>45957</v>
+      </c>
+      <c r="D45">
+        <v>4707.66</v>
+      </c>
+      <c r="E45">
+        <v>59.86</v>
+      </c>
+      <c r="F45">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="G45">
+        <v>4766.74</v>
+      </c>
+      <c r="H45">
+        <v>8595.26</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>300</v>
+      </c>
+      <c r="K45">
+        <v>8295.26</v>
+      </c>
+      <c r="L45">
+        <v>13062</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>4676.16</v>
+      </c>
+      <c r="E46">
+        <v>511.44</v>
+      </c>
+      <c r="F46">
+        <v>30</v>
+      </c>
+      <c r="G46">
+        <v>5157.599999999999</v>
+      </c>
+      <c r="H46">
+        <v>8035.45</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>8035.45</v>
+      </c>
+      <c r="L46">
+        <v>13193.05</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>4929.81</v>
+      </c>
+      <c r="E47">
+        <v>106.67</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>5036.48</v>
+      </c>
+      <c r="H47">
+        <v>2704.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>2704.3</v>
+      </c>
+      <c r="L47">
+        <v>7740.780000000001</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>2590.8</v>
+      </c>
+      <c r="E48">
+        <v>120</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>2710.8</v>
+      </c>
+      <c r="H48">
+        <v>1003.34</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1003.34</v>
+      </c>
+      <c r="L48">
+        <v>3714.14</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
